--- a/docs/triton-learning/cards/triton-lesson-07-extern-functions-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-07-extern-functions-correction.xlsx
@@ -41,55 +41,86 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">给一个逐元素的 Triton kernel 写 Python 包装函数 asin(x)：kernel 的参数依次是输入指针、输出指针、元素个数和 BLOCK_SIZE。约定要求返回一个新张量，并且不修改输入。包装函数应该怎样把张量传给 kernel？</t>
+          <t xml:space="preserve">在 Triton 3.7.1 中写一个 asin kernel：同一个 kernel 要支持 fp16、bf16、fp32、fp64 四种指针类型，fp64 要保持双精度计算。用 tl.load 读出 x_data 之后，调用 libdevice.asin 这一步应该怎样写？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 07 课练习的首次提交。kernel 本身已经写好，问题出在包装函数的调用和返回上；这个错误只有 GPU 上的数值测试能测到。</t>
+          <t xml:space="preserve">写练习 kernel 时的代码；相关规则此前在讲解和复查题里都答对过。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">先用 torch.empty_like(x) 新建输出 y，调用 asin_kernel\[grid\](x, y, n, BLOCK_SIZE)，最后 return y。</t>
+          <t xml:space="preserve">在 kernel 内按 x_data 的类型处理：fp16、bf16 先 .to(tl.float32) 再调用（选中 __nv_asinf），fp32、fp64 直接调用（fp64 仍选中 __nv_asin）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">asin_kernel\[grid\](x, x, n, BLOCK_SIZE, extern_libs=extern_libs)，函数也没有 return</t>
+          <t xml:space="preserve">res = libdevice.asin(x_data)（四种指针类型都直接这样调用）</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：把同一个张量既当输入又当输出，kernel 会原地覆盖调用者的数据；没有 return，调用方拿到的是 None。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：fp32、fp64 这样写没问题，错在 fp16、bf16 也直接传给了 libdevice：asin 的表里只有 fp32 和 fp64 两项，半精度在编译期查表就失败，报 KeyError。
+• [T#B#查表]：后端实现里的每个 libdevice 函数是一张“参数 dtype 元组 → (符号名, 返回 dtype)”的表；extern_elementwise 在编译期按实参的 dtype 精确查表，查到就在 TTIR 里生成一条带符号名的 tt.extern_elementwise，查不到就失败，不做隐式提升。多参数函数的键是所有参数 dtype 组成的元组，例如 pow(bf16, fp32) 同样报 KeyError。
+• [T#B#为什么不自动提升]：这是有意的约定：很多加速器不支持半精度的数学运算，升精度带来的开销和精度变化应由写 kernel 的人显式决定。
+• [T#B#写回]：结果是 fp32，tl.store 写入半精度指针时会自动转成指针的元素类型，不必手写转回。
+[T#B,!c47f17#边界]：tl.math 的超越函数（exp、log、sin、sqrt、erf 等）同样只收 fp32、fp64，但不符时报的是 ValueError；sqrt_rn、div_rn 只收 fp32。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">为逐元素 kernel asin_kernel(x_ptr, y_ptr, n_elements, BLOCK_SIZE) 写 Python 包装函数 asin(x, *, extern_libs=None)，用法和 torch.asin(x) 一样，extern_libs 要原样传给 kernel。包装函数里启动 kernel 的那一行和返回值应该怎样写？</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kernel 已通过只编译测试；包装函数要到 GPU 上真正启动时才会被测到。</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y = torch.empty_like(x)；asin_kernel\[grid\](x, y, n, BLOCK_SIZE, extern_libs=extern_libs)；return y</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asin_kernel\[grid\](x, x, n, BLOCK_SIZE, extern_libs=extern_libs)，函数也没有 return</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错在输出与返回：extern_libs 原样透传没有问题，但把 x 同时当输出会原地覆盖调用者的数据；没有 return，调用方拿到的是 None。
 • [T#B#为什么本机没发现]：只编译的测试只检查 kernel，包装函数的行为要到 GPU 上真正启动时才暴露；这一处是读代码时发现的。
 • [T#B#自查办法]：对照约定逐条核对包装函数：输出是否新分配，是否返回，输入在调用前后是否相同。
 [T#B,!c47f17#边界]：有些算子有意提供原地版本，那需要在接口上写明；默认约定是不修改输入。</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">同一个 Triton kernel 要按输入指针的元素类型选择不同处理：fp16、bf16 先升到 fp32，fp64 保持不变。kernel 应该从哪里得到“元素类型是什么”这个信息？</t>
+          <t xml:space="preserve">Triton 3.7.1 中，同一个 kernel 要按输入指针的元素类型选择不同处理：fp16、bf16 先升到 fp32，fp64 保持不变。kernel 应该从哪里得到“元素类型是什么”这个信息？</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 07 课练习的第二次提交。分派逻辑是对的，四种类型都能选中正确的符号；问题在于类型信息的来源和 kernel 的接口。</t>
+          <t xml:space="preserve">分派逻辑本身是对的，四种类型都能选中正确的符号。</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">用加载结果自身的 dtype 做编译期分支，例如判断 x_data.dtype；kernel 不需要额外的参数。</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">给 kernel 加 is_bf16: tl.constexpr 和 is_fp16: tl.constexpr 两个参数，由包装函数传入</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：指针的类型已经包含元素类型，再传标志是重复信息，而重复的信息可能互相矛盾。
 • [T#B#实测]：fp32 指针配 is_fp16=True 能通过编译，结果先被截成 fp16 再转回 fp32，精度被悄悄丢掉；fp64 指针同理。
@@ -98,45 +129,15 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Triton kernel 里先把半精度的 x_data 转成 fp32 去调用 libdevice，算完后想把结果转回原来的半精度类型再写出。转回这一步应该怎么处理？</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">第 07 课练习的第三次提交。测试全部通过，但读代码发现有几行分支永远不会执行。</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">不需要手动转回：tl.store 写入时会自动把值转成指针的元素类型。</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">在 x_data = x_data.to(tl.float32) 之后写 if x_data.dtype == tl.bfloat16: res = res.to(tl.bfloat16)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：判断的是变量当前绑定的值；x_data 已经被换成 fp32 版本，再判断它是不是 bfloat16，永远不成立。
-• [T#B#证据]：编译产物里那条 fp32 转半精度的指令，对应的源码位置是 tl.store 那一行，而不是手写的转换。
-• [T#B#如果确实要判断]：要么在覆盖变量之前把原类型的判断保存成 constexpr，要么用另一个变量名存放升精度后的值。
-[T#B,!c47f17#边界]：结果正确不等于每一行都在起作用；这类不会执行的代码要靠读编译产物才能发现。</t>
-        </is>
-      </c>
-    </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">向面试官口述 Triton 的编译流程时，从 TTGIR 到 LLVM IR 这一步由谁完成？LLVM 从哪里开始接手？</t>
+          <t xml:space="preserve">向面试官口述 Triton 3.7.1 的编译流程时，从 TTGIR 到 LLVM IR 这一步由谁完成？LLVM 从哪里开始接手？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 07 课综合验收的口述题，条件是 fp16 输入、调用 libdevice.erf、目标为 AMD 后端。全链路的顺序和“链接加内联所以没有调用”都答对了。</t>
+          <t xml:space="preserve">60–90 秒的口述题：fp16 输入、调用 libdevice.erf、目标为 AMD 后端。全链路的顺序和“链接加内联所以没有调用”都答对了。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -151,9 +152,8 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：把张量操作拆成每个线程的标量代码，是 Triton 的降级代码做的；LLVM 拿到的已经是 LLVM IR。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错在把 TTGIR 到 LLVM IR 的转换归给了 LLVM：把张量操作拆成每个线程的标量代码，是 Triton 自己的降级代码做的；LLVM 拿到的已经是 LLVM IR。
 • [T#B#为什么要分清]：逐元素调用怎样生成属于 Triton 的公共代码，所有后端共用；链接哪个库、怎样内联，才是各后端在 LLVM 阶段填的内容。
-• [T#B#同题的另一处遗漏]：题目给了 fp16 输入，口述里要说到必须先在 kernel 里转成 fp32，否则在查表处就报 KeyError；AMD 上符号是 __ocml_erf_f32，每个 warp 64 个线程。
 [T#B,!c47f17#边界]：链接和 O3 由后端代码调用 LLVM 的功能完成，把它们说成 LLVM 阶段没有问题；错的只是把转换也归给 LLVM。</t>
         </is>
       </c>
@@ -161,17 +161,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">同一个调用 libdevice.asin 的 Triton kernel，对输入 1e-40，NVIDIA 输出 0，AMD 输出约 1e-40。想让两个后端的结果一致，各应调整哪个选项？</t>
+          <t xml:space="preserve">Triton 3.7.1 中，同一个调用 libdevice.asin 的 kernel 对输入 1e-40，NVIDIA 输出 0，AMD 输出约 1e-40。想让两个后端的结果一致，各应调整哪个选项？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 07 课综合验收的诊断题。对 NVIDIA 一侧的原因答对了：生成 PTX 时按反射参数选定是否冲掉次正规数。</t>
+          <t xml:space="preserve">诊断题；kernel 里只有 libdevice.asin 一处数学调用，其余元素两边一致。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NVIDIA 传 enable_reflect_ftz=False，让两边都保留；或者 AMD 传 allow_flush_denorm=True，让两边都冲成 0。</t>
+          <t xml:space="preserve">NVIDIA 传 enable_reflect_ftz=False，让两边都保留；或者 AMD 传 allow_flush_denorm=True，让两边都清零。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -181,11 +181,10 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：两个后端控制次正规数的机制不同，默认值也相反；enable_reflect_ftz 只是 NVIDIA 一侧的选项。
-• [T#B#AMD]：AMD 不用反射参数，靠 kernel 函数上的属性控制，选项 allow_flush_denorm 默认是 False，也就是默认保留。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：错在两处：只给了 NVIDIA 一侧的选项，又把 enable_reflect_ftz 的影响说成了所有可能出现次正规数的计算。两个后端控制次正规数的机制不同，默认值也相反。
+• [T#B#AMD]：AMD 不用反射参数，靠 kernel 函数上的属性 denormal-fp-math-f32 控制，对应选项 allow_flush_denorm，默认 False，也就是默认保留。
 • [T#B#影响范围]：enable_reflect_ftz 只影响这个 kernel 里 libdevice 函数内部的代码，Triton 自己生成的指令不受它影响。
-• [T#B#传错选项的现象]：真实启动 AMD 的 kernel 时传 enable_reflect_ftz，会直接报不认识的关键字参数，而不是静默无效。
-[T#B,!c47f17#边界]：AMD 一侧的默认值来自阅读源码和只编译的观察，没有在真实设备上验证数值。</t>
+[T#B,!c47f17#边界]：两个开关的作用范围不对称：AMD 的属性挂在整个 kernel 函数上，NVIDIA 的反射参数只作用于 libdevice 内部；kernel 里还有别的浮点运算时，两种改法未必等价。AMD 一侧只有读源码和只编译的观察。</t>
         </is>
       </c>
     </row>
